--- a/DateBase/orders/Nhat 48_2026-6-13.xlsx
+++ b/DateBase/orders/Nhat 48_2026-6-13.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>628_多丁白星太子_undefined_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0121211010201114110</v>
+        <v>0121211010201114115</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-6-13.xlsx
+++ b/DateBase/orders/Nhat 48_2026-6-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,9 +524,96 @@
         <v>5</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F12" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="C13" t="str" xml:space="preserve">
+        <v xml:space="preserve">448_吊米 绿_hanging amaranthus
+green_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3</v>
+      </c>
+      <c r="C15" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F15" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>4</v>
+      </c>
+      <c r="C16" t="str">
+        <v>462_五针松_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>118_绣球老绿_Hydrangea Garden Lace_Hydrangea L._1stem</v>
+      </c>
+      <c r="F17" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>540_糖棉_gomphocarpus fruticosus_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>5</v>
+      </c>
+      <c r="C20" t="str">
+        <v>788_直葱_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>771_美洲茶_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +668,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0121211010201114115</v>
+        <v>01212110102011141151562071530310150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-6-13.xlsx
+++ b/DateBase/orders/Nhat 48_2026-6-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -610,10 +610,21 @@
       <c r="C21" t="str">
         <v>771_美洲茶_undefined_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>792_珍珠梅白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L22"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -668,7 +679,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01212110102011141151562071530310150</v>
+        <v>01212110102011141151562071530310151010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-6-13.xlsx
+++ b/DateBase/orders/Nhat 48_2026-6-13.xlsx
@@ -616,7 +616,7 @@
     </row>
     <row r="22">
       <c r="C22" t="str">
-        <v>792_珍珠梅白_undefined_undefined_1bunch</v>
+        <v>793_珍珠梅粉_undefined_undefined_1bunch</v>
       </c>
       <c r="F22" t="str">
         <v>10</v>
